--- a/upload/PLANTILLA_CARGA_DATOS_TRAZASOLE_v3.7.24 - MARCELO.xlsx
+++ b/upload/PLANTILLA_CARGA_DATOS_TRAZASOLE_v3.7.24 - MARCELO.xlsx
@@ -9,12 +9,15 @@
   <sheets>
     <sheet name="TROPAS" sheetId="7" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">TROPAS!$A$1:$K$221</definedName>
+  </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="786">
   <si>
     <t>TROPAS</t>
   </si>
@@ -2288,6 +2291,90 @@
   </si>
   <si>
     <t>D-08</t>
+  </si>
+  <si>
+    <t>B 2026 0200</t>
+  </si>
+  <si>
+    <t>B 2026 0201</t>
+  </si>
+  <si>
+    <t>B 2026 0202</t>
+  </si>
+  <si>
+    <t>B 2026 0203</t>
+  </si>
+  <si>
+    <t>B 2026 0204</t>
+  </si>
+  <si>
+    <t>B 2026 0205</t>
+  </si>
+  <si>
+    <t>B 2026 0206</t>
+  </si>
+  <si>
+    <t>B 2026 0207</t>
+  </si>
+  <si>
+    <t>B 2026 0208</t>
+  </si>
+  <si>
+    <t>LLORENTE ARSENIO FERNANDO</t>
+  </si>
+  <si>
+    <t>20-07393573-4</t>
+  </si>
+  <si>
+    <t>31829840-8</t>
+  </si>
+  <si>
+    <t>G-CHO26-02822</t>
+  </si>
+  <si>
+    <t>31829952-8</t>
+  </si>
+  <si>
+    <t>G-CHO26-02824</t>
+  </si>
+  <si>
+    <t>31822816-7</t>
+  </si>
+  <si>
+    <t>G-CHO26-02815</t>
+  </si>
+  <si>
+    <t>31838395-2</t>
+  </si>
+  <si>
+    <t>D-03-D-04</t>
+  </si>
+  <si>
+    <t>31849558-0</t>
+  </si>
+  <si>
+    <t>G-CHO26-02882</t>
+  </si>
+  <si>
+    <t>31857425-1</t>
+  </si>
+  <si>
+    <t>G-CHO26-02912</t>
+  </si>
+  <si>
+    <t>31857546-0</t>
+  </si>
+  <si>
+    <t>G-CHO26-02913</t>
+  </si>
+  <si>
+    <t>31854965-6</t>
+  </si>
+  <si>
+    <t>G-CHO26-00072</t>
+  </si>
+  <si>
+    <t>31855363-7</t>
   </si>
 </sst>
 </file>
@@ -2385,7 +2472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2457,6 +2544,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2760,7 +2848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K204"/>
+  <dimension ref="A1:K212"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -2787,19 +2875,19 @@
       <c r="K1" s="8"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
     </row>
     <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -9799,8 +9887,319 @@
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A204" s="3"/>
-      <c r="B204" s="14"/>
+      <c r="A204" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="B204" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C204" t="s">
+        <v>179</v>
+      </c>
+      <c r="D204" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="E204" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F204" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="G204" s="11" t="s">
+        <v>771</v>
+      </c>
+      <c r="H204" s="10" t="s">
+        <v>772</v>
+      </c>
+      <c r="I204" s="21">
+        <v>12</v>
+      </c>
+      <c r="J204" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K204" s="15">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="B205" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C205" s="31" t="s">
+        <v>767</v>
+      </c>
+      <c r="D205" s="31" t="s">
+        <v>768</v>
+      </c>
+      <c r="E205" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F205" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="G205" s="11" t="s">
+        <v>769</v>
+      </c>
+      <c r="H205" s="10" t="s">
+        <v>770</v>
+      </c>
+      <c r="I205" s="21">
+        <v>21</v>
+      </c>
+      <c r="J205" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="K205" s="15">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A206" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="B206" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C206" t="s">
+        <v>308</v>
+      </c>
+      <c r="D206" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="E206" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="F206" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G206" s="11" t="s">
+        <v>773</v>
+      </c>
+      <c r="H206" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="I206" s="21">
+        <v>30</v>
+      </c>
+      <c r="J206" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="K206" s="15">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A207" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="B207" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C207" t="s">
+        <v>208</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+      <c r="E207" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F207" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G207" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="H207" s="10">
+        <v>9296629</v>
+      </c>
+      <c r="I207" s="21">
+        <v>30</v>
+      </c>
+      <c r="J207" s="12" t="s">
+        <v>776</v>
+      </c>
+      <c r="K207" s="15">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A208" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="B208" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C208" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="D208" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="E208" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F208" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="G208" s="11" t="s">
+        <v>777</v>
+      </c>
+      <c r="H208" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="I208" s="21">
+        <v>12</v>
+      </c>
+      <c r="J208" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K208" s="15">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A209" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="B209" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C209" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="D209" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="E209" s="10" t="s">
+        <v>679</v>
+      </c>
+      <c r="F209" s="31" t="s">
+        <v>680</v>
+      </c>
+      <c r="G209" s="11" t="s">
+        <v>779</v>
+      </c>
+      <c r="H209" s="10" t="s">
+        <v>780</v>
+      </c>
+      <c r="I209" s="21">
+        <v>4</v>
+      </c>
+      <c r="J209" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="K209" s="15">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A210" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="B210" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C210" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="D210" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="E210" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="F210" s="31" t="s">
+        <v>671</v>
+      </c>
+      <c r="G210" s="11" t="s">
+        <v>781</v>
+      </c>
+      <c r="H210" s="10" t="s">
+        <v>782</v>
+      </c>
+      <c r="I210" s="21">
+        <v>2</v>
+      </c>
+      <c r="J210" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="K210" s="15">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A211" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="B211" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C211" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="D211" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="E211" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F211" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="G211" s="11" t="s">
+        <v>783</v>
+      </c>
+      <c r="H211" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="I211" s="21">
+        <v>15</v>
+      </c>
+      <c r="J211" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="K211" s="15">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A212" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="B212" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C212" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="D212" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="E212" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F212" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G212" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="H212" s="10">
+        <v>419109</v>
+      </c>
+      <c r="I212" s="21">
+        <v>10</v>
+      </c>
+      <c r="J212" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="K212" s="15">
+        <v>46168</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
